--- a/avgo/dist/20261025_Broadcom模型_v0.1.1.xlsx
+++ b/avgo/dist/20261025_Broadcom模型_v0.1.1.xlsx
@@ -3502,7 +3502,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -3795,7 +3795,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4092,7 +4092,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4243,7 +4243,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4414,7 +4414,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4565,7 +4565,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4727,7 +4727,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -4954,7 +4954,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5166,7 +5166,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5317,7 +5317,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5574,7 +5574,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5725,7 +5725,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -5887,7 +5887,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6038,7 +6038,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6278,7 +6278,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6646,7 +6646,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6770,7 +6770,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6988,7 +6988,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7109,7 +7109,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7230,7 +7230,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7351,7 +7351,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7472,7 +7472,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10260,7 +10260,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10636,7 +10636,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -10934,7 +10934,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.4.2.xlsx</t>
+      <t xml:space="preserve">_v0.5.xlsx</t>
     </r>
     <r>
       <rPr>
